--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104697_W27.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104697_W27.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9961</v>
+        <v>8.3467</v>
       </c>
       <c r="E2" t="n">
-        <v>5.493</v>
+        <v>6.0102</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5031</v>
+        <v>2.3365</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4086</v>
+        <v>5.3999</v>
       </c>
       <c r="H2" t="n">
-        <v>2.218</v>
+        <v>2.2091</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1906</v>
+        <v>3.1908</v>
       </c>
       <c r="J2" t="n">
-        <v>5.921</v>
+        <v>5.8698</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9513</v>
+        <v>3.9193</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9697</v>
+        <v>1.9505</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5124</v>
+        <v>-0.4699</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7334</v>
+        <v>-1.7102</v>
       </c>
       <c r="O2" t="n">
-        <v>1.221</v>
+        <v>1.2402</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2368</v>
+        <v>0.1337</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.5303</v>
+        <v>-0.9412</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2935</v>
+        <v>1.0749</v>
       </c>
       <c r="V2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="W2" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3962</v>
+        <v>4.8785</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4589</v>
+        <v>2.522</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9374</v>
+        <v>2.3565</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3064</v>
+        <v>1.2919</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9785</v>
+        <v>0.9657</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3278</v>
+        <v>0.3262</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2856</v>
+        <v>2.2344</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3338</v>
+        <v>2.3023</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0481</v>
+        <v>-0.0679</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9792</v>
+        <v>-0.9425</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3552</v>
+        <v>-1.3365</v>
       </c>
       <c r="O3" t="n">
-        <v>0.376</v>
+        <v>0.3941</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1825</v>
+        <v>0.6761</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4657</v>
+        <v>-0.3466</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6483</v>
+        <v>1.0226</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9916</v>
+        <v>4.5435</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6676</v>
+        <v>4.9979</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.676</v>
+        <v>-0.4544</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5553</v>
+        <v>3.5585</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9467</v>
+        <v>-0.9368</v>
       </c>
       <c r="I4" t="n">
-        <v>4.502</v>
+        <v>4.4954</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4792</v>
+        <v>4.4593</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6345</v>
       </c>
       <c r="L4" t="n">
-        <v>5.1097</v>
+        <v>5.0938</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.764</v>
+        <v>-0.223</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9043</v>
+        <v>-0.5508</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1403</v>
+        <v>0.3278</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2991</v>
+        <v>3.5104</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2073</v>
+        <v>0.8707</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0918</v>
+        <v>2.6397</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4039</v>
+        <v>1.4132</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1661</v>
+        <v>-0.1584</v>
       </c>
       <c r="I5" t="n">
-        <v>1.57</v>
+        <v>1.5716</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8418</v>
+        <v>1.8122</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5514</v>
+        <v>1.5373</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2904</v>
+        <v>0.2749</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4379</v>
+        <v>-0.399</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7175</v>
+        <v>-1.6957</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2796</v>
+        <v>1.2967</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4263</v>
+        <v>-0.2184</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4608</v>
+        <v>-0.7531</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0345</v>
+        <v>0.5347</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4393</v>
+        <v>1.2627</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2002</v>
+        <v>0.7694</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6395</v>
+        <v>0.4933</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8884</v>
+        <v>1.2102</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.4586</v>
+        <v>0.2613</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5701</v>
+        <v>0.9489</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2823</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.1033</v>
+        <v>0.2758</v>
       </c>
       <c r="L6" t="n">
-        <v>0.821</v>
+        <v>0.633</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6061</v>
+        <v>0.3014</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3552</v>
+        <v>-0.0144</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7492</v>
+        <v>0.3159</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.5878</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3939</v>
+        <v>-0.0174</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9629</v>
+        <v>-0.1394</v>
       </c>
       <c r="U6" t="n">
-        <v>0.431</v>
+        <v>0.122</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7071</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2275</v>
+        <v>-0.0535</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7723</v>
+        <v>-1.8914</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4552</v>
+        <v>1.8379</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2101</v>
+        <v>-1.886</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2612</v>
+        <v>-3.4716</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9489</v>
+        <v>1.5856</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9115</v>
+        <v>-1.3159</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2771</v>
+        <v>-2.1351</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6344</v>
+        <v>0.8192</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2986</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0159</v>
+        <v>-1.3365</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3145</v>
+        <v>0.7664</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.5934</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0487</v>
+        <v>0.9024</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1391</v>
+        <v>0.3154</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.587</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1607</v>
+        <v>0.7025</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5848</v>
+        <v>-0.5167</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0174</v>
+        <v>1.0142</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6022</v>
+        <v>-1.5309</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4179</v>
+        <v>-0.4122</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9856</v>
+        <v>-0.9797</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5678</v>
+        <v>0.5675</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2261</v>
+        <v>1.2233</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1568</v>
+        <v>1.1543</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.644</v>
+        <v>-1.6355</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0549</v>
+        <v>-1.0487</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1669</v>
+        <v>-0.1046</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0417</v>
+        <v>0.1046</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,22 +1111,22 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.5946</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2087</v>
+        <v>-0.0907</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.5039</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.7315</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1138,28 +1138,28 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.7315</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2087</v>
+        <v>-0.0907</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2087</v>
+        <v>-0.0907</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1935</v>
+        <v>-2.3561</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6159</v>
+        <v>-1.8741</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5776</v>
+        <v>-0.482</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0646</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6494</v>
+        <v>-1.6459</v>
       </c>
       <c r="I10" t="n">
-        <v>1.714</v>
+        <v>1.7193</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9458</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0591</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>1.0048</v>
+        <v>0.9977</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8812</v>
+        <v>-0.8587</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5903</v>
+        <v>-1.5802</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7091</v>
+        <v>0.7215</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5831</v>
+        <v>0.4112</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1603</v>
+        <v>-0.0746</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4228</v>
+        <v>0.4857</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0735</v>
+        <v>-3.169</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6611</v>
+        <v>-1.67</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4124</v>
+        <v>-1.499</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0623</v>
+        <v>-1.0634</v>
       </c>
       <c r="H11" t="n">
         <v>0.3131</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3754</v>
+        <v>-1.3765</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4573</v>
+        <v>-0.4621</v>
       </c>
       <c r="K11" t="n">
-        <v>0.329</v>
+        <v>0.3275</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.605</v>
+        <v>-0.6012</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2156</v>
+        <v>0.122</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2852</v>
+        <v>0.1917</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1173</v>
+        <v>-4.1799</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0818</v>
+        <v>-3.0977</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0355</v>
+        <v>-1.0822</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2609</v>
+        <v>-0.2543</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1357</v>
+        <v>-0.1323</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1253</v>
+        <v>-0.122</v>
       </c>
       <c r="J12" t="n">
-        <v>0.738</v>
+        <v>0.735</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5888</v>
+        <v>0.5861</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.999</v>
+        <v>-0.9893</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7245</v>
+        <v>-0.7184</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0417</v>
+        <v>-0.1046</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4174</v>
+        <v>-0.4182</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3756</v>
+        <v>0.3137</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.6635</v>
+        <v>11.672</v>
       </c>
       <c r="E13" t="n">
-        <v>7.848800000000002</v>
+        <v>7.560500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>3.814699999999999</v>
+        <v>4.111499999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>8.584</v>
+        <v>8.599699999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.090800000000001</v>
+        <v>-4.092600000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>12.6746</v>
+        <v>12.6924</v>
       </c>
       <c r="J13" t="n">
-        <v>16.6094</v>
+        <v>16.3968</v>
       </c>
       <c r="K13" t="n">
-        <v>6.307799999999999</v>
+        <v>6.1819</v>
       </c>
       <c r="L13" t="n">
-        <v>10.3016</v>
+        <v>10.2148</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.025500000000001</v>
+        <v>-7.796999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.3985</v>
+        <v>-10.2744</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3731</v>
+        <v>2.4774</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.134300000000001</v>
+        <v>-1.138299999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.61</v>
+        <v>-13.658</v>
       </c>
       <c r="R13" t="n">
-        <v>12.4758</v>
+        <v>12.5197</v>
       </c>
       <c r="S13" t="n">
-        <v>1.482</v>
+        <v>1.4867</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.281400000000001</v>
+        <v>-3.278000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>4.7633</v>
+        <v>4.764699999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>2.731700000000001</v>
+        <v>2.723599999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>8.1309</v>
+        <v>8.0997</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.3992</v>
+        <v>-5.375900000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4719</v>
+        <v>6.9115</v>
       </c>
       <c r="E14" t="n">
-        <v>6.4415</v>
+        <v>6.6295</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0304</v>
+        <v>0.282</v>
       </c>
       <c r="G14" t="n">
-        <v>4.1322</v>
+        <v>4.1137</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3491</v>
+        <v>2.3493</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7831</v>
+        <v>1.7644</v>
       </c>
       <c r="J14" t="n">
-        <v>5.4584</v>
+        <v>5.4185</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3421</v>
+        <v>3.3267</v>
       </c>
       <c r="L14" t="n">
-        <v>2.1162</v>
+        <v>2.0918</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3261</v>
+        <v>-1.3048</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.993</v>
+        <v>-0.9774</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5677</v>
+        <v>-0.1127</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5898</v>
+        <v>-0.3534</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0221</v>
+        <v>0.2407</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="15">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9489</v>
+        <v>0.9196</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5392</v>
+        <v>0.5364</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4097</v>
+        <v>0.3832</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6915</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5556</v>
+        <v>0.5544</v>
       </c>
       <c r="I15" t="n">
-        <v>0.136</v>
+        <v>0.1387</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6088</v>
+        <v>0.6061</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5715</v>
+        <v>0.5688</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0828</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O15" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2574</v>
+        <v>0.2265</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3269</v>
+        <v>0.2962</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4994</v>
+        <v>0.2331</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0897</v>
+        <v>0.385</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5903</v>
+        <v>-0.1519</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2475</v>
+        <v>2.0773</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5513</v>
+        <v>1.9939</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3038</v>
+        <v>0.0835</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6514</v>
+        <v>3.607</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4648</v>
+        <v>2.2818</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1866</v>
+        <v>1.3252</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4039</v>
+        <v>-1.5296</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9135</v>
+        <v>-0.2879</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4904</v>
+        <v>-1.2417</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6805</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-2.5039</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9324</v>
+        <v>-0.4784</v>
       </c>
       <c r="T16" t="n">
-        <v>0.614</v>
+        <v>-0.718</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3185</v>
+        <v>0.2396</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1798</v>
+        <v>-0.068</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3143</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4941</v>
+        <v>-0.6623</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0885</v>
+        <v>0.2468</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0059</v>
+        <v>0.546</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.2992</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6442</v>
+        <v>1.6373</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3062</v>
+        <v>1.4511</v>
       </c>
       <c r="L17" t="n">
-        <v>1.338</v>
+        <v>0.1862</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5557</v>
+        <v>-1.3906</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3003</v>
+        <v>-0.9052</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2554</v>
+        <v>-0.4854</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.361</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4952</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9073</v>
+        <v>0.3681</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8347</v>
+        <v>0.1438</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0726</v>
+        <v>0.2243</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4951</v>
+        <v>-0.65</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8133</v>
+        <v>-0.7228</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3183</v>
+        <v>0.0728</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.6069</v>
+        <v>-3.6085</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5383</v>
+        <v>-1.5285</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.0685</v>
+        <v>-2.08</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2467</v>
+        <v>-1.2707</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0417</v>
+        <v>-0.0485</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.205</v>
+        <v>-1.2223</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3602</v>
+        <v>-2.3378</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4966</v>
+        <v>-1.48</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0723</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6593</v>
+        <v>-0.5415</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7316</v>
+        <v>0.4498</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="19">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7473</v>
+        <v>-1.4795</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.106</v>
+        <v>-0.4821</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6413</v>
+        <v>-0.9974</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4606</v>
+        <v>-2.4598</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.792</v>
+        <v>-0.8008</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6685</v>
+        <v>-1.659</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6967</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6967</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7639</v>
+        <v>-1.7457</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6685</v>
+        <v>-1.659</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6206</v>
+        <v>-0.1092</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0484</v>
+        <v>-0.4021</v>
       </c>
       <c r="U19" t="n">
-        <v>0.669</v>
+        <v>0.2929</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9336</v>
+        <v>-1.8175</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4553</v>
+        <v>-1.2478</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4783</v>
+        <v>-0.5698</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1136</v>
+        <v>-0.1055</v>
       </c>
       <c r="H20" t="n">
-        <v>2.5439</v>
+        <v>2.5473</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.6575</v>
+        <v>-2.6528</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0848</v>
+        <v>1.0662</v>
       </c>
       <c r="K20" t="n">
-        <v>2.5456</v>
+        <v>2.5338</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1984</v>
+        <v>-1.1717</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0017</v>
+        <v>0.0135</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4343</v>
+        <v>-0.3251</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.113</v>
+        <v>-0.8784</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6787</v>
+        <v>0.5532</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1252</v>
+        <v>-1.908</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.71</v>
+        <v>-1.7255</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4151</v>
+        <v>-0.1825</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2248</v>
+        <v>-1.224</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.7379</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9592</v>
+        <v>-1.9619</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2976</v>
+        <v>-0.3085</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6407</v>
+        <v>0.6378</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.9383</v>
+        <v>-0.9463</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9272</v>
+        <v>-0.9155</v>
       </c>
       <c r="N21" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4467</v>
+        <v>-0.2287</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2782</v>
+        <v>-0.2788</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1685</v>
+        <v>0.0501</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0437</v>
+        <v>-3.7978</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0028</v>
+        <v>-0.9162</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.041</v>
+        <v>-2.8816</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.354</v>
+        <v>-0.353</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9351</v>
+        <v>-0.9308</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.5778</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3321</v>
+        <v>1.307</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.603</v>
+        <v>-0.614</v>
       </c>
       <c r="L22" t="n">
-        <v>1.9351</v>
+        <v>1.921</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6861</v>
+        <v>-1.6599</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8239</v>
+        <v>-0.583</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9739</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.15</v>
+        <v>0.2744</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2949</v>
+        <v>-4.3257</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1883</v>
+        <v>-2.4382</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1066</v>
+        <v>-1.8875</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2791</v>
+        <v>-3.2663</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2266</v>
+        <v>-1.2182</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.0524</v>
+        <v>-2.048</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6761</v>
+        <v>-0.6864</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0764</v>
+        <v>-0.0829</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5998</v>
+        <v>-0.6035</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.6029</v>
+        <v>-2.5799</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1503</v>
+        <v>-1.1353</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.15</v>
+        <v>-0.1977</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1512</v>
+        <v>-0.386</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0012</v>
+        <v>0.1884</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7641</v>
+        <v>-5.6895</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.9236</v>
+        <v>-4.724</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8405</v>
+        <v>-0.9655</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.7047</v>
+        <v>-4.7135</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1573</v>
+        <v>-0.1579</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.5475</v>
+        <v>-4.5556</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.8372</v>
+        <v>-2.8652</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9453</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.7825</v>
+        <v>-3.7993</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8675</v>
+        <v>-1.8483</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0348</v>
+        <v>0.0452</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6593</v>
+        <v>-0.4231</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.4683</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.6635</v>
+        <v>-11.6718</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.814600000000001</v>
+        <v>-4.1114</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.848800000000001</v>
+        <v>-7.560499999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-8.584</v>
+        <v>-8.599800000000002</v>
       </c>
       <c r="H25" t="n">
-        <v>4.090899999999999</v>
+        <v>4.092600000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-12.6746</v>
+        <v>-12.6921</v>
       </c>
       <c r="J25" t="n">
-        <v>8.025400000000001</v>
+        <v>7.797099999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>10.3984</v>
+        <v>10.2744</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.3732</v>
+        <v>-2.4776</v>
       </c>
       <c r="M25" t="n">
-        <v>-16.6091</v>
+        <v>-16.3968</v>
       </c>
       <c r="N25" t="n">
-        <v>-6.3077</v>
+        <v>-6.181900000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-10.3015</v>
+        <v>-10.215</v>
       </c>
       <c r="P25" t="n">
-        <v>1.1341</v>
+        <v>1.1381</v>
       </c>
       <c r="Q25" t="n">
-        <v>-12.4758</v>
+        <v>-12.5197</v>
       </c>
       <c r="R25" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.482</v>
+        <v>-1.4868</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.7634</v>
+        <v>-4.7646</v>
       </c>
       <c r="U25" t="n">
-        <v>3.2814</v>
+        <v>3.2779</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.7317</v>
+        <v>-2.7236</v>
       </c>
       <c r="W25" t="n">
-        <v>5.3992</v>
+        <v>5.376099999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.130899999999999</v>
+        <v>-8.099600000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104697_W27.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104697_W27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-5.375900000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104697_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-8.099600000000001</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
